--- a/mosip_master/xlsx/daysofweek_list.xlsx
+++ b/mosip_master/xlsx/daysofweek_list.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kames\IdeaProjects\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SLUDI Offline Training\mosip-data-1.3.0\mosip-data-1.3.0\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A513C33-8793-45B8-8F3A-D789DAF30086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A14C785C-4777-48AF-A715-ED1AA54F8535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$29</definedName>
+  </definedNames>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="47">
   <si>
     <t>lang_code</t>
   </si>
@@ -75,123 +78,33 @@
     <t>SAT</t>
   </si>
   <si>
-    <t>fra</t>
-  </si>
-  <si>
-    <t>DIM</t>
-  </si>
-  <si>
     <t>LUN</t>
   </si>
   <si>
     <t>MAR</t>
   </si>
   <si>
-    <t>MER</t>
-  </si>
-  <si>
-    <t>JEU</t>
-  </si>
-  <si>
-    <t>VEN</t>
-  </si>
-  <si>
-    <t>SAM</t>
-  </si>
-  <si>
-    <t>ara</t>
-  </si>
-  <si>
     <t>101</t>
   </si>
   <si>
-    <t>الشمس</t>
-  </si>
-  <si>
     <t>102</t>
   </si>
   <si>
-    <t>الإثنين</t>
-  </si>
-  <si>
     <t>103</t>
   </si>
   <si>
-    <t>الثلاثاء</t>
-  </si>
-  <si>
     <t>104</t>
   </si>
   <si>
-    <t>تزوج</t>
-  </si>
-  <si>
     <t>105</t>
   </si>
   <si>
-    <t>خميس</t>
-  </si>
-  <si>
     <t>106</t>
   </si>
   <si>
-    <t>الجمعة</t>
-  </si>
-  <si>
     <t>107</t>
   </si>
   <si>
-    <t>جلس</t>
-  </si>
-  <si>
-    <t>kan</t>
-  </si>
-  <si>
-    <t>ಸೂರ್ಯ</t>
-  </si>
-  <si>
-    <t>ಸೋಮ</t>
-  </si>
-  <si>
-    <t>ಮಂಗಳ</t>
-  </si>
-  <si>
-    <t>ಬುಧ</t>
-  </si>
-  <si>
-    <t>ಗುರು</t>
-  </si>
-  <si>
-    <t>ಶುಕ್ರ</t>
-  </si>
-  <si>
-    <t>ಶನಿ</t>
-  </si>
-  <si>
-    <t>hin</t>
-  </si>
-  <si>
-    <t>रवि</t>
-  </si>
-  <si>
-    <t>सोमवार</t>
-  </si>
-  <si>
-    <t>मंगल</t>
-  </si>
-  <si>
-    <t>बुध</t>
-  </si>
-  <si>
-    <t>इकट्ठा करना</t>
-  </si>
-  <si>
-    <t>शुक्र</t>
-  </si>
-  <si>
-    <t>बैठा</t>
-  </si>
-  <si>
     <t>tam</t>
   </si>
   <si>
@@ -232,6 +145,30 @@
   </si>
   <si>
     <t>SE SENTÓ</t>
+  </si>
+  <si>
+    <t>sin</t>
+  </si>
+  <si>
+    <t>ඉරිදා</t>
+  </si>
+  <si>
+    <t>සඳුදා</t>
+  </si>
+  <si>
+    <t>අඟහරුවාදා</t>
+  </si>
+  <si>
+    <t>බදාදා</t>
+  </si>
+  <si>
+    <t>බ්‍රහස්පතින්දා</t>
+  </si>
+  <si>
+    <t>සිකුරාදා</t>
+  </si>
+  <si>
+    <t>සෙනසුරාදා</t>
   </si>
 </sst>
 </file>
@@ -617,14 +554,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F50"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="8.453125" style="1"/>
-    <col min="5" max="6" width="8.453125" style="1"/>
+    <col min="2" max="2" width="8.44140625" style="1"/>
+    <col min="5" max="6" width="8.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -644,7 +581,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -664,7 +601,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -684,7 +621,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -704,7 +641,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -724,7 +661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -744,7 +681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -764,7 +701,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -784,15 +721,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1">
         <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -804,15 +741,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1">
         <v>102</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -824,15 +761,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B11" s="1">
         <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -844,15 +781,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B12" s="1">
         <v>104</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D12">
         <v>4</v>
@@ -864,15 +801,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B13" s="1">
         <v>105</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -884,15 +821,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B14" s="1">
         <v>106</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -904,15 +841,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="1">
-        <v>107</v>
+        <v>25</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D15">
         <v>7</v>
@@ -924,15 +861,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -944,15 +881,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -964,15 +901,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -984,15 +921,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D19">
         <v>4</v>
@@ -1004,15 +941,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D20">
         <v>5</v>
@@ -1024,15 +961,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D21">
         <v>6</v>
@@ -1044,12 +981,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="C22" t="s">
         <v>38</v>
@@ -1064,7 +1001,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -1084,7 +1021,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -1104,7 +1041,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -1124,7 +1061,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -1144,7 +1081,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -1164,7 +1101,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -1184,7 +1121,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -1204,429 +1141,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>47</v>
-      </c>
-      <c r="B30" s="1">
-        <v>101</v>
-      </c>
-      <c r="C30" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>47</v>
-      </c>
-      <c r="B31" s="1">
-        <v>102</v>
-      </c>
-      <c r="C31" t="s">
-        <v>49</v>
-      </c>
-      <c r="D31">
-        <v>2</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>47</v>
-      </c>
-      <c r="B32" s="1">
-        <v>103</v>
-      </c>
-      <c r="C32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D32">
-        <v>3</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>47</v>
-      </c>
-      <c r="B33" s="1">
-        <v>104</v>
-      </c>
-      <c r="C33" t="s">
-        <v>51</v>
-      </c>
-      <c r="D33">
-        <v>4</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>47</v>
-      </c>
-      <c r="B34" s="1">
-        <v>105</v>
-      </c>
-      <c r="C34" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34">
-        <v>5</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>47</v>
-      </c>
-      <c r="B35" s="1">
-        <v>106</v>
-      </c>
-      <c r="C35" t="s">
-        <v>53</v>
-      </c>
-      <c r="D35">
-        <v>6</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>47</v>
-      </c>
-      <c r="B36" s="1">
-        <v>107</v>
-      </c>
-      <c r="C36" t="s">
-        <v>54</v>
-      </c>
-      <c r="D36">
-        <v>7</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" s="1">
-        <v>101</v>
-      </c>
-      <c r="C37" t="s">
-        <v>56</v>
-      </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>55</v>
-      </c>
-      <c r="B38" s="1">
-        <v>102</v>
-      </c>
-      <c r="C38" t="s">
-        <v>57</v>
-      </c>
-      <c r="D38">
-        <v>2</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>55</v>
-      </c>
-      <c r="B39" s="1">
-        <v>103</v>
-      </c>
-      <c r="C39" t="s">
-        <v>58</v>
-      </c>
-      <c r="D39">
-        <v>3</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>55</v>
-      </c>
-      <c r="B40" s="1">
-        <v>104</v>
-      </c>
-      <c r="C40" t="s">
-        <v>59</v>
-      </c>
-      <c r="D40">
-        <v>4</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>55</v>
-      </c>
-      <c r="B41" s="1">
-        <v>105</v>
-      </c>
-      <c r="C41" t="s">
-        <v>60</v>
-      </c>
-      <c r="D41">
-        <v>5</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>55</v>
-      </c>
-      <c r="B42" s="1">
-        <v>106</v>
-      </c>
-      <c r="C42" t="s">
-        <v>61</v>
-      </c>
-      <c r="D42">
-        <v>6</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>55</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C43" t="s">
-        <v>62</v>
-      </c>
-      <c r="D43">
-        <v>7</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>63</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C44" t="s">
-        <v>64</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>63</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C45" t="s">
-        <v>18</v>
-      </c>
-      <c r="D45">
-        <v>2</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>63</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C46" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46">
-        <v>3</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>63</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" t="s">
-        <v>65</v>
-      </c>
-      <c r="D47">
-        <v>4</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>63</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C48" t="s">
-        <v>66</v>
-      </c>
-      <c r="D48">
-        <v>5</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>63</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C49" t="s">
-        <v>67</v>
-      </c>
-      <c r="D49">
-        <v>6</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>63</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C50" t="s">
-        <v>68</v>
-      </c>
-      <c r="D50">
-        <v>7</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:F29" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>